--- a/sant_cugat_offer_candidates_400_700k.xlsx
+++ b/sant_cugat_offer_candidates_400_700k.xlsx
@@ -7774,7 +7774,7 @@
         <v>0.08799999999999999</v>
       </c>
       <c r="O43" t="n">
-        <v>62.8</v>
+        <v>62.9</v>
       </c>
       <c r="P43" t="n">
         <v>2</v>
